--- a/test/MD95-2042.xlsx
+++ b/test/MD95-2042.xlsx
@@ -8,15 +8,15 @@
   </bookViews>
   <sheets>
     <sheet name="Information" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Serie Id-1FB8C5DF" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Serie Id-1FDB2383" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Serie Id-6198B9AF" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Serie Id-3B2BB420" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Serie Id-125575B2" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Serie Id-16C67B7D" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Serie Id-E001AEC2" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Series Id-1FB8C5DF" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Series Id-1FDB2383" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Series Id-6198B9AF" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Series Id-3B2BB420" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Series Id-125575B2" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Series Id-16C67B7D" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Series Id-E001AEC2" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="INTERPOLATION Id-784A2BB4" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Serie Id-947891E7" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Series Id-947891E7" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -431,7 +431,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Created with PyAnalyseries v5.11</t>
+          <t>Created with PyAnalyseries v5.43</t>
         </is>
       </c>
     </row>
@@ -447,6 +447,14 @@
       <c r="A4" t="inlineStr">
         <is>
           <t>Do not modify or accordingly with documentation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Saved 2025/12/22 at 16:55:56</t>
         </is>
       </c>
     </row>
@@ -464,14 +472,14 @@
   <dimension ref="A1:H102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="147" customWidth="1" min="8" max="8"/>
+    <col width="144" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -497,12 +505,12 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Y axis inverted</t>
+          <t>Color</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Color</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -525,22 +533,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Serie</t>
+          <t>Series</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>#17becf</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>&lt;BR&gt;Random serie with parameters :&lt;ul&gt;&lt;li&gt;Start point : 0&lt;li&gt;End point : 100&lt;li&gt;Nb of points : 101&lt;li&gt;Min value : 10.0&lt;li&gt;Max value : 0.0&lt;/ul&gt;</t>
+          <t>Random series with parameters :&lt;ul&gt;&lt;li&gt;Start point : 0&lt;li&gt;End point : 100&lt;li&gt;Nb of points : 101&lt;li&gt;Min value : 10.0&lt;li&gt;Max value : 0.0&lt;/ul&gt;</t>
         </is>
       </c>
     </row>
@@ -1360,10 +1366,10 @@
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
@@ -1391,12 +1397,12 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Y axis inverted</t>
+          <t>Color</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Color</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -1419,18 +1425,16 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Serie</t>
+          <t>Series</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>#c7c7c7</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
@@ -3926,10 +3930,10 @@
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
@@ -3957,12 +3961,12 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Y axis inverted</t>
+          <t>Color</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Color</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -3985,18 +3989,16 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Serie</t>
+          <t>Series</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>#2d9edb</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
@@ -9284,10 +9286,10 @@
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
@@ -9315,12 +9317,12 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Y axis inverted</t>
+          <t>Color</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Color</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -9343,18 +9345,16 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Serie</t>
+          <t>Series</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
-          <t>#8c564b</t>
+          <t>#8c5773</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
@@ -14850,10 +14850,10 @@
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
@@ -14881,12 +14881,12 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Y axis inverted</t>
+          <t>Color</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Color</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -14909,18 +14909,16 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Serie</t>
+          <t>Series</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>#98df8a</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
@@ -21320,10 +21318,10 @@
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
@@ -21351,12 +21349,12 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Y axis inverted</t>
+          <t>Color</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Color</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -21379,18 +21377,16 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Serie</t>
+          <t>Series</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>#ff9896</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
@@ -26886,12 +26882,12 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="143" customWidth="1" min="8" max="8"/>
+    <col width="144" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -26917,12 +26913,12 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Y axis inverted</t>
+          <t>Color</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Color</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -26945,22 +26941,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Serie</t>
+          <t>Series</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>#c5b0d5</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Insolation serie "Daily insolation" with parameters:&lt;ul&gt;&lt;li&gt;Solar constant [W/m2]: 1365&lt;li&gt;Latitude [°]: 65&lt;li&gt;True longitude [°]: 90&lt;/ul&gt;</t>
+          <t>Insolation series "Daily insolation" with parameters:&lt;ul&gt;&lt;li&gt;Solar constant [W/m2]: 1365&lt;li&gt;Latitude [°]: 65&lt;li&gt;True longitude [°]: 90&lt;/ul&gt;</t>
         </is>
       </c>
     </row>
@@ -34980,12 +34974,12 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="43" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -35011,12 +35005,12 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Y axis inverted</t>
+          <t>Color</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Color</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -35039,22 +35033,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Serie</t>
+          <t>Series</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>#ff9896</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Astronomical serie "Precession angle"</t>
+          <t>Astronomical series "Precession angle"</t>
         </is>
       </c>
     </row>
@@ -43069,7 +43061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -43077,8 +43069,9 @@
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -43109,10 +43102,15 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>Comment</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>History</t>
         </is>
@@ -43142,6 +43140,7 @@
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
